--- a/Dataset/1_label/DOWN_DOWN_V4_33 divisions_per_second.xlsx
+++ b/Dataset/1_label/DOWN_DOWN_V4_33 divisions_per_second.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1688,6 +1688,24 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>constant_velocity</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>DOWN_DOWN_V4_33 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
           <t>steady</t>
         </is>
       </c>
